--- a/SLR/Full-Paper-Read/Paper-Review/PS07.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS07.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -26,70 +26,84 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>The study aims to catalouge through a mapping study the practices of automotive software engineering, motivated by the change from hardware to software centric development. 679 articles are analysed. RQ1: What is the intensity of research on automotive software engineering? RQ2: What are the msot frequenctly invistaegated research topics? RQ3: What are the most frequently applied research types? RQ4: What kind of contributions are provided by studies? RQ5: What are the research gaps? Following research themes and challenges: Theme 1. Comprehensive automotive architectureTheme 2. Reducing complexity
-• Theme 3. Improving development processes
-• Theme 4. Seamless model-driven development
-• Theme 5. Integrated tool support
-• Theme 6. Learning from other domains
-• Theme 7. Improving quality and reliability
-• Theme 8. Standardized automotive software and system infras_x0002_tructure
-The paper answers the RQs and provide nuanced commentary on all of the topics.</t>
-  </si>
-  <si>
-    <t>The mapping study is not directly linked with out study, but there are some interesting outputs as it is linked with software engineering. However, most of the data points in the review protocol are not relevant for this study.</t>
+    <t>The paper outlines essential standardization activities, real-time Big Data processing approaches, and necessary analytical tools, emphasizing that IoT's evolution relies on collaboration between standardization organizations, open-source communities, and IT experts.
+Verifying data and metadata, including their provenance and sensor locations, poses additional challenges, necessitating detailed modeling of these interconnected elements.
+Effective business integration requires both vertical integration of technical and business processes and horizontal integration across company boundaries, encompassing the entire value chain.
+IoT and Big Data technologies originate from distinct backgrounds. IoT is primarily hardware-driven, while Big Data has roots in software paradigms developed by internet and social media giants like Google, Facebook, and Yahoo. Both hardware and software are integral to enabling data-driven IoT solutions. The paper addresses software concepts and platforms essential for managing large-scale IoT data, highlighting the need for robust analytical tools to unlock deeper data value.
+IoT offers significant opportunities, supported by the open-source Hadoop ecosystem, accepted exchange formats, and expanding standards. This convergence of platforms suggests a future where IoT seamlessly integrates into various aspects of life, driven by continuous innovation and standardization.</t>
+  </si>
+  <si>
+    <t>User requirements
+Data sovereignty The data owner specifies the terms and conditions of use for data
+Decentral data management Data management remains with the data owner, if desired
+Data economy Data is viewed as an economic asset. It can be distinguished into three categories: private data, i.e., data
+belonging to a specific value creation chain, which is available to selected companies only, and public data
+(weather or traffic information, geo data etc.)
+Value creation The IDS facilitates the creation and use of smart services and digital business models
+Easy linkage of data Linked-data concepts and common vocabularies facilitate the integration of data between participants
+Trust All participants, data sources, and data services of the IDS are certified against commonly defined rules
+Secure data supply chain Data exchange is secure across the entire data supply chain, i.e. from data creation to data capture to data usage
+Data governance Participants jointly decide on data management processes as well as on applicable rights and dutie</t>
   </si>
   <si>
     <t>CPS Case Study / Example availability</t>
   </si>
   <si>
+    <t>n.a.</t>
+  </si>
+  <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
-    <t>N</t>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Several platforms/tools/standards/soution alternatives, IoT platforms in the cloud (e.g., Ayla or Cumulocity), </t>
   </si>
   <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
-    <t>Modeling and Model-Driven Engineering</t>
-  </si>
-  <si>
-    <t>Continuous software and system engineering</t>
-  </si>
-  <si>
-    <t>n.a.</t>
-  </si>
-  <si>
-    <t>Architecture, testing, software re-use</t>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Intelligence and automation</t>
+  </si>
+  <si>
+    <t>Integration, security</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
   </si>
   <si>
-    <t>Maybe partially? The authors mention automotive software ecosystem, and tools, frameworks, approaches, and challenges relate to automotive domain, for me it answer partially, while it focus on automotive domain and list technical and research papers dealing with software ecosystems.
-The authors said: "Several other miscellaneous subjects, such as development and maintenance of automotive reference architecture [P129, P218,
-P35], architecture for supporting federated embedded systems and ecosystems [P90, P276, P88], and architecture for innovative experimental systems [P211, P91], were also discussed in the literature". See also Table A11.</t>
+    <t>A lot of talk about buisness, value chain, new personell, new roles, bridging silos, etc.</t>
   </si>
   <si>
     <t>Does the paper present methods, tools, and benefits in terms of industry/academia collaboration? If so, write what methods, tools, and benefits in the comment column</t>
   </si>
   <si>
+    <t>The paper presents different organization working on the integration of software ecosystems. It presents the German industrial associations that defines a framework (i.e., Reference Architecture Modell Industry 4.0 - RAMI 4.0) in Industry 4.0, the industrial data space (IDS) initiative and its reference architecture, and the Industrial internet consortium (IIC) and the W3C web of things interest group, with the WebOfThings interaction model. finally, it presents the Hadoop ecosystem, with the open source Apache Hadoop software library is the most prominent open source framework that allows for the distributed processing of large, structured and unstructured datasets across clusters of computers. DATA: The Hadoop ecosystem is gradually turning into a general-purpose data-operating system and is the leading framework for dealing with an extraordinary influx of datasets, often with a need to compute in real-time.</t>
+  </si>
+  <si>
     <t>Does it contribute to answer RQ2?</t>
   </si>
   <si>
+    <t>More related to DATA.</t>
+  </si>
+  <si>
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Automotive</t>
+    <t>Application Domain Independent</t>
+  </si>
+  <si>
+    <t>Industry 4.0, cloud</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
-  </si>
-  <si>
-    <t>The study quality is very high since they follow clear guidelines for systematic studies, but I still think the study is not very valuable for us since there is nothing to do with software eco-systems nor industry academia collaboration</t>
   </si>
   <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
@@ -565,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -601,10 +615,10 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="17" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -613,17 +627,14 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="19" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="20" fillId="4" fontId="1" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -635,7 +646,7 @@
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -668,6 +679,9 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -679,19 +693,16 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
     <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
@@ -962,7 +973,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="2.5"/>
-    <col customWidth="1" min="2" max="2" width="62.38"/>
+    <col customWidth="1" min="2" max="2" width="46.13"/>
     <col customWidth="1" min="3" max="3" width="9.0"/>
     <col customWidth="1" min="4" max="4" width="9.88"/>
     <col customWidth="1" min="5" max="5" width="9.0"/>
@@ -1009,7 +1020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="229.5" customHeight="1">
+    <row r="3" ht="243.0" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="12"/>
@@ -1027,8 +1038,8 @@
       <c r="B4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="17">
-        <v>0.0</v>
+      <c r="C4" s="17" t="s">
+        <v>7</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1036,7 +1047,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1044,10 +1055,10 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
@@ -1055,7 +1066,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1063,28 +1074,28 @@
         <v>4.0</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -1092,10 +1103,10 @@
         <v>5.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -1103,7 +1114,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="23" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1111,18 +1122,18 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="27" t="s">
-        <v>7</v>
+      <c r="I8" s="23" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1130,10 +1141,10 @@
         <v>7.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>9</v>
+        <v>20</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>10</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -1141,7 +1152,7 @@
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
       <c r="I9" s="21" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1149,28 +1160,28 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>7</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1178,30 +1189,30 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="31">
+        <v>25</v>
+      </c>
+      <c r="C11" s="30">
         <f>Quality!C29</f>
-        <v>8.888888889</v>
+        <v>3.888888889</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="32" t="s">
-        <v>22</v>
+      <c r="I11" s="31" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="B14" s="33" t="s">
-        <v>23</v>
+      <c r="B14" s="32" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="B15" s="33" t="s">
-        <v>24</v>
+      <c r="B15" s="32" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
@@ -2260,83 +2271,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="36"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
+      <c r="A1" s="33"/>
+      <c r="B1" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="35"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37"/>
     </row>
     <row r="2">
-      <c r="A2" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="41">
+      <c r="A2" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="40">
         <v>1.0</v>
       </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="42"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3">
-      <c r="A3" s="43"/>
-      <c r="B3" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="41">
+      <c r="A3" s="42"/>
+      <c r="B3" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="40">
         <v>1.0</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="42"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4">
-      <c r="A4" s="43"/>
-      <c r="B4" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
     </row>
     <row r="5">
-      <c r="A5" s="43"/>
-      <c r="B5" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
+      <c r="A5" s="42"/>
+      <c r="B5" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
     </row>
     <row r="6">
-      <c r="A6" s="43"/>
-      <c r="B6" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="41">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
     </row>
     <row r="7">
       <c r="A7" s="44"/>
-      <c r="B7" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="41">
-        <v>1.0</v>
+      <c r="B7" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="43">
+        <v>0.5</v>
       </c>
       <c r="D7" s="45">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
@@ -2344,139 +2355,139 @@
       </c>
       <c r="E7" s="45">
         <f>(SUM(C2:C7)/D7)*10</f>
-        <v>10</v>
+        <v>6.666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="46" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="42"/>
+      <c r="B9" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="42"/>
+      <c r="B10" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="42"/>
+      <c r="B11" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="42"/>
+      <c r="B12" s="47" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="42"/>
+      <c r="B13" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="42"/>
+      <c r="B14" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="42"/>
+      <c r="B15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="48">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="42"/>
+      <c r="B16" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="42"/>
+      <c r="B17" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="48">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="42"/>
+      <c r="B18" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="49">
         <v>1.0</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="43"/>
-      <c r="B9" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="43"/>
-      <c r="B10" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="43"/>
-      <c r="B11" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="49">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="43"/>
-      <c r="B12" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="43"/>
-      <c r="B13" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="43"/>
-      <c r="B14" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="43"/>
-      <c r="B15" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="43"/>
-      <c r="B16" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="43"/>
-      <c r="B17" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="43"/>
-      <c r="B18" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="48">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
     </row>
     <row r="19">
       <c r="A19" s="44"/>
       <c r="B19" s="47" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="49">
-        <v>0.5</v>
+        <v>49</v>
+      </c>
+      <c r="C19" s="48">
+        <v>0.0</v>
       </c>
       <c r="D19" s="45">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
@@ -2484,138 +2495,138 @@
       </c>
       <c r="E19" s="45">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>8.75</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C20" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
     </row>
     <row r="21">
-      <c r="A21" s="43"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="51" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C21" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
     </row>
     <row r="22">
-      <c r="A22" s="43"/>
+      <c r="A22" s="42"/>
       <c r="B22" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="53">
+        <v>53</v>
+      </c>
+      <c r="C22" s="52">
         <v>0.5</v>
       </c>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
     </row>
     <row r="23">
-      <c r="A23" s="43"/>
+      <c r="A23" s="42"/>
       <c r="B23" s="51" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C23" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="42"/>
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="41"/>
     </row>
     <row r="24">
-      <c r="A24" s="43"/>
+      <c r="A24" s="42"/>
       <c r="B24" s="51" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C24" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="42"/>
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="41"/>
     </row>
     <row r="25">
       <c r="A25" s="44"/>
       <c r="B25" s="51" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C25" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="53">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="53">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>9.166666667</v>
-      </c>
-      <c r="F25" s="42"/>
+        <v>3.333333333</v>
+      </c>
+      <c r="F25" s="41"/>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="57">
+      <c r="A26" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="56">
         <v>1.0</v>
       </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="42"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="41"/>
     </row>
     <row r="27">
-      <c r="A27" s="43"/>
-      <c r="B27" s="56" t="s">
-        <v>56</v>
+      <c r="A27" s="42"/>
+      <c r="B27" s="55" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="57">
-        <v>1.0</v>
-      </c>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="42"/>
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="41"/>
     </row>
     <row r="28">
       <c r="A28" s="44"/>
-      <c r="B28" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="58">
+      <c r="B28" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="57">
         <v>0.0</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="53">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="53">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="F28" s="42"/>
+        <v>5</v>
+      </c>
+      <c r="F28" s="41"/>
     </row>
     <row r="29">
-      <c r="B29" s="59">
+      <c r="B29" s="58">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="58">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>8.888888889</v>
+        <v>3.888888889</v>
       </c>
     </row>
   </sheetData>
